--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/ILLINOIS_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/ILLINOIS_2016.xlsx
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C133">
@@ -3541,7 +3541,7 @@
         <v>596</v>
       </c>
       <c r="D177">
-        <v>0.009401224051990661</v>
+        <v>0.00940122405199066</v>
       </c>
     </row>
     <row r="178">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C190">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C345">
@@ -6871,7 +6871,7 @@
         <v>60</v>
       </c>
       <c r="D362">
-        <v>0.0009464319515426841</v>
+        <v>0.000946431951542684</v>
       </c>
     </row>
     <row r="363">
@@ -10471,7 +10471,7 @@
         <v>59</v>
       </c>
       <c r="D562">
-        <v>0.0009306580856836393</v>
+        <v>0.0009306580856836392</v>
       </c>
     </row>
     <row r="563">
@@ -13729,7 +13729,7 @@
         <v>59</v>
       </c>
       <c r="D743">
-        <v>0.0009306580856836393</v>
+        <v>0.0009306580856836392</v>
       </c>
     </row>
     <row r="744">
@@ -15162,7 +15162,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C823">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C825">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C826">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C940">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C978">
@@ -26826,7 +26826,7 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1471">
@@ -28291,7 +28291,7 @@
         <v>60</v>
       </c>
       <c r="D1552">
-        <v>0.0009464319515426841</v>
+        <v>0.000946431951542684</v>
       </c>
     </row>
     <row r="1553">
@@ -30685,7 +30685,7 @@
         <v>59</v>
       </c>
       <c r="D1685">
-        <v>0.0009306580856836393</v>
+        <v>0.0009306580856836392</v>
       </c>
     </row>
     <row r="1686">
